--- a/Data/final_tables/supplementary_table_1_BARD1_OddsRatios_table.xlsx
+++ b/Data/final_tables/supplementary_table_1_BARD1_OddsRatios_table.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ivan/Documents/GitHub/BARD1_SGE_analysis/Data/final_tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D0EDF3-C414-614D-A985-FC73115D424C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07FF1C91-A673-CA4F-9376-AED755A0369D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="README" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>

--- a/Data/final_tables/supplementary_table_1_BARD1_OddsRatios_table.xlsx
+++ b/Data/final_tables/supplementary_table_1_BARD1_OddsRatios_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ivan/Documents/GitHub/BARD1_SGE_analysis/Data/final_tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07FF1C91-A673-CA4F-9376-AED755A0369D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A0D47CF-AD0E-DF44-884C-335DA9595105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="141">
   <si>
     <t>Cohort</t>
   </si>
@@ -405,9 +405,6 @@
   </si>
   <si>
     <t>Cohort from which cases/controls were pulled from. Either carriers or bridges.  When cohorts were combined, they are specified as Cohort1+cohort2</t>
-  </si>
-  <si>
-    <t>Datset</t>
   </si>
   <si>
     <t>Data used from respective cohort. Either 'all', 'pop', or 'cc_pop_er_cases'. 'all' denotes all variants. 'pop' denotes data only from population-based studies. 'cc_pop_er-cases' denotes ER negative cases pulled from the CARRIERS cohort</t>
@@ -841,10 +838,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -852,7 +849,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -860,7 +857,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -868,7 +865,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -876,7 +873,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -884,7 +881,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -892,7 +889,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -900,7 +897,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -908,7 +905,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -916,7 +913,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -924,7 +921,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
@@ -932,7 +929,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -940,7 +937,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
